--- a/ch_02_pandas/ch_02.xlsx
+++ b/ch_02_pandas/ch_02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\python-in-excel-book-staging\new_datasets\ch_02_pandas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_02_pandas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E789429D-51CE-46B4-A0EE-0F9BE053541E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E7D40BD-D687-4419-9C90-BB9448128F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nyc" sheetId="1" r:id="rId1"/>
@@ -741,7 +741,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -762,6 +762,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -784,37 +790,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <b/>
@@ -846,18 +833,6 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{36148E99-D7FB-436D-B1F1-8BC8952D7B3C}" name="nyc_pop" displayName="nyc_pop" ref="A1:C6" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:C6" xr:uid="{36148E99-D7FB-436D-B1F1-8BC8952D7B3C}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{FFC8B188-1AB7-4C04-992E-BD927F255738}" name="borough"/>
-    <tableColumn id="2" xr3:uid="{ADC4FF43-EFC0-4FAB-82F1-80173E26348F}" name="population" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{482FC98B-A0D9-473A-A5FF-D449571E48D0}" name="land_area"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{21C6BCE0-7690-49D4-8544-F73EB21401D5}" name="sales" displayName="sales" ref="A1:G201" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="A1:G201" xr:uid="{21C6BCE0-7690-49D4-8544-F73EB21401D5}"/>
   <tableColumns count="7">
@@ -1159,73 +1134,73 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="14" style="4" customWidth="1"/>
+    <col min="2" max="2" width="14" style="3" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="3">
         <v>1694251</v>
       </c>
       <c r="C2">
         <v>22.83</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>2736074</v>
       </c>
       <c r="C3">
         <v>69.37</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>2405464</v>
       </c>
       <c r="C4">
         <v>108.53</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>1472654</v>
       </c>
       <c r="C5">
         <v>42.1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="3">
         <v>495747</v>
       </c>
       <c r="C6">
@@ -1234,16 +1209,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G201"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -1254,7 +1226,7 @@
     <col min="7" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -1277,7 +1249,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -1300,7 +1272,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -1323,7 +1295,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1346,7 +1318,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1369,7 +1341,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -1392,7 +1364,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1415,7 +1387,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -1438,7 +1410,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -1461,7 +1433,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -1484,7 +1456,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -1507,7 +1479,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -1530,7 +1502,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -1553,7 +1525,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1576,7 +1548,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1599,7 +1571,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1622,7 +1594,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -1645,7 +1617,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1668,7 +1640,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -1691,7 +1663,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -1714,7 +1686,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>51</v>
       </c>
@@ -1737,7 +1709,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -1760,7 +1732,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1783,7 +1755,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1806,7 +1778,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -1829,7 +1801,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1852,7 +1824,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1875,7 +1847,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>61</v>
       </c>
@@ -1898,7 +1870,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>62</v>
       </c>
@@ -1921,7 +1893,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1944,7 +1916,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>64</v>
       </c>
@@ -1967,7 +1939,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1990,7 +1962,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -2013,7 +1985,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>68</v>
       </c>
@@ -2036,7 +2008,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>69</v>
       </c>
@@ -2059,7 +2031,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>70</v>
       </c>
@@ -2082,7 +2054,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>71</v>
       </c>
@@ -2105,7 +2077,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>73</v>
       </c>
@@ -2128,7 +2100,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>74</v>
       </c>
@@ -2151,7 +2123,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>75</v>
       </c>
@@ -2174,7 +2146,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>77</v>
       </c>
@@ -2197,7 +2169,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>78</v>
       </c>
@@ -2220,7 +2192,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>79</v>
       </c>
@@ -2243,7 +2215,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>80</v>
       </c>
@@ -2266,7 +2238,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>81</v>
       </c>
@@ -2289,7 +2261,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>82</v>
       </c>
@@ -2312,7 +2284,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>83</v>
       </c>
@@ -2335,7 +2307,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>84</v>
       </c>
@@ -2358,7 +2330,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>85</v>
       </c>
@@ -2381,7 +2353,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>86</v>
       </c>
@@ -2404,7 +2376,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>87</v>
       </c>
@@ -2427,7 +2399,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>88</v>
       </c>
@@ -2450,7 +2422,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>89</v>
       </c>
@@ -2473,7 +2445,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>90</v>
       </c>
@@ -2496,7 +2468,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>91</v>
       </c>
@@ -2519,7 +2491,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>92</v>
       </c>
@@ -2542,7 +2514,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>93</v>
       </c>
@@ -2565,7 +2537,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>94</v>
       </c>
@@ -2588,7 +2560,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>95</v>
       </c>
@@ -2611,7 +2583,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>96</v>
       </c>
@@ -2634,7 +2606,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>97</v>
       </c>
@@ -2657,7 +2629,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -2680,7 +2652,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>99</v>
       </c>
@@ -2703,7 +2675,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -2726,7 +2698,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>101</v>
       </c>
@@ -2749,7 +2721,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>102</v>
       </c>
@@ -2769,7 +2741,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>103</v>
       </c>
@@ -2792,7 +2764,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>104</v>
       </c>
@@ -2815,7 +2787,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>105</v>
       </c>
@@ -2838,7 +2810,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>106</v>
       </c>
@@ -2861,7 +2833,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>107</v>
       </c>
@@ -2884,7 +2856,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>108</v>
       </c>
@@ -2907,7 +2879,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>109</v>
       </c>
@@ -2930,7 +2902,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>110</v>
       </c>
@@ -2953,7 +2925,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>111</v>
       </c>
@@ -2976,7 +2948,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>112</v>
       </c>
@@ -2999,7 +2971,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>113</v>
       </c>
@@ -3022,7 +2994,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>114</v>
       </c>
@@ -3045,7 +3017,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>115</v>
       </c>
@@ -3068,7 +3040,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>116</v>
       </c>
@@ -3091,7 +3063,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>117</v>
       </c>
@@ -3114,7 +3086,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>118</v>
       </c>
@@ -3137,7 +3109,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>119</v>
       </c>
@@ -3160,7 +3132,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>120</v>
       </c>
@@ -3183,7 +3155,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>121</v>
       </c>
@@ -3206,7 +3178,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>122</v>
       </c>
@@ -3229,7 +3201,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>123</v>
       </c>
@@ -3252,7 +3224,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>124</v>
       </c>
@@ -3275,7 +3247,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>125</v>
       </c>
@@ -3298,7 +3270,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>126</v>
       </c>
@@ -3321,7 +3293,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>127</v>
       </c>
@@ -3344,7 +3316,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>128</v>
       </c>
@@ -3367,7 +3339,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>129</v>
       </c>
@@ -3390,7 +3362,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>130</v>
       </c>
@@ -3413,7 +3385,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>131</v>
       </c>
@@ -3436,7 +3408,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>132</v>
       </c>
@@ -3459,7 +3431,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>133</v>
       </c>
@@ -3482,7 +3454,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>134</v>
       </c>
@@ -3505,7 +3477,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>135</v>
       </c>
@@ -3528,7 +3500,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>136</v>
       </c>
@@ -3551,7 +3523,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>137</v>
       </c>
@@ -3574,7 +3546,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>138</v>
       </c>
@@ -3597,7 +3569,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>139</v>
       </c>
@@ -3620,7 +3592,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>140</v>
       </c>
@@ -3643,7 +3615,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>141</v>
       </c>
@@ -3666,7 +3638,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>142</v>
       </c>
@@ -3689,7 +3661,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>143</v>
       </c>
@@ -3712,7 +3684,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>144</v>
       </c>
@@ -3735,7 +3707,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>145</v>
       </c>
@@ -3758,7 +3730,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>146</v>
       </c>
@@ -3781,7 +3753,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>147</v>
       </c>
@@ -3804,7 +3776,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>148</v>
       </c>
@@ -3827,7 +3799,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>149</v>
       </c>
@@ -3850,7 +3822,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>150</v>
       </c>
@@ -3873,7 +3845,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>151</v>
       </c>
@@ -3896,7 +3868,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>152</v>
       </c>
@@ -3919,7 +3891,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>153</v>
       </c>
@@ -3942,7 +3914,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>154</v>
       </c>
@@ -3965,7 +3937,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>155</v>
       </c>
@@ -3988,7 +3960,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>156</v>
       </c>
@@ -4011,7 +3983,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>157</v>
       </c>
@@ -4034,7 +4006,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>158</v>
       </c>
@@ -4057,7 +4029,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>159</v>
       </c>
@@ -4080,7 +4052,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>160</v>
       </c>
@@ -4103,7 +4075,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>161</v>
       </c>
@@ -4126,7 +4098,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>162</v>
       </c>
@@ -4149,7 +4121,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>163</v>
       </c>
@@ -4172,7 +4144,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>164</v>
       </c>
@@ -4192,7 +4164,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>165</v>
       </c>
@@ -4215,7 +4187,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>166</v>
       </c>
@@ -4238,7 +4210,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>167</v>
       </c>
@@ -4261,7 +4233,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>168</v>
       </c>
@@ -4284,7 +4256,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>169</v>
       </c>
@@ -4307,7 +4279,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>170</v>
       </c>
@@ -4330,7 +4302,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>171</v>
       </c>
@@ -4353,7 +4325,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>172</v>
       </c>
@@ -4376,7 +4348,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>173</v>
       </c>
@@ -4399,7 +4371,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>174</v>
       </c>
@@ -4422,7 +4394,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>175</v>
       </c>
@@ -4445,7 +4417,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>176</v>
       </c>
@@ -4468,7 +4440,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>177</v>
       </c>
@@ -4491,7 +4463,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>178</v>
       </c>
@@ -4514,7 +4486,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>179</v>
       </c>
@@ -4537,7 +4509,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>180</v>
       </c>
@@ -4560,7 +4532,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>181</v>
       </c>
@@ -4583,7 +4555,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>182</v>
       </c>
@@ -4606,7 +4578,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>183</v>
       </c>
@@ -4629,7 +4601,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>184</v>
       </c>
@@ -4652,7 +4624,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>185</v>
       </c>
@@ -4672,7 +4644,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>186</v>
       </c>
@@ -4695,7 +4667,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>187</v>
       </c>
@@ -4718,7 +4690,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>188</v>
       </c>
@@ -4741,7 +4713,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>189</v>
       </c>
@@ -4764,7 +4736,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>190</v>
       </c>
@@ -4787,7 +4759,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>191</v>
       </c>
@@ -4810,7 +4782,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>192</v>
       </c>
@@ -4830,7 +4802,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>193</v>
       </c>
@@ -4853,7 +4825,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>194</v>
       </c>
@@ -4876,7 +4848,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>195</v>
       </c>
@@ -4899,7 +4871,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>196</v>
       </c>
@@ -4922,7 +4894,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>197</v>
       </c>
@@ -4945,7 +4917,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>198</v>
       </c>
@@ -4968,7 +4940,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>199</v>
       </c>
@@ -4991,7 +4963,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>200</v>
       </c>
@@ -5011,7 +4983,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>201</v>
       </c>
@@ -5034,7 +5006,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>202</v>
       </c>
@@ -5057,7 +5029,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>203</v>
       </c>
@@ -5080,7 +5052,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>204</v>
       </c>
@@ -5103,7 +5075,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>205</v>
       </c>
@@ -5126,7 +5098,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>206</v>
       </c>
@@ -5149,7 +5121,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>207</v>
       </c>
@@ -5172,7 +5144,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>208</v>
       </c>
@@ -5195,7 +5167,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>209</v>
       </c>
@@ -5215,7 +5187,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>210</v>
       </c>
@@ -5238,7 +5210,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>211</v>
       </c>
@@ -5261,7 +5233,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>212</v>
       </c>
@@ -5284,7 +5256,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>213</v>
       </c>
@@ -5307,7 +5279,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>214</v>
       </c>
@@ -5330,7 +5302,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>215</v>
       </c>
@@ -5353,7 +5325,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>216</v>
       </c>
@@ -5376,7 +5348,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>217</v>
       </c>
@@ -5399,7 +5371,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>218</v>
       </c>
@@ -5422,7 +5394,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>219</v>
       </c>
@@ -5445,7 +5417,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>220</v>
       </c>
@@ -5468,7 +5440,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>221</v>
       </c>
@@ -5491,7 +5463,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>222</v>
       </c>
@@ -5514,7 +5486,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>223</v>
       </c>
@@ -5537,7 +5509,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>224</v>
       </c>
@@ -5560,7 +5532,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>225</v>
       </c>
@@ -5583,7 +5555,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>226</v>
       </c>
@@ -5606,7 +5578,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>227</v>
       </c>
@@ -5629,7 +5601,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>228</v>
       </c>
@@ -5652,7 +5624,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>229</v>
       </c>
@@ -5675,7 +5647,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>230</v>
       </c>
@@ -5698,7 +5670,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>231</v>
       </c>
@@ -5721,7 +5693,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>232</v>
       </c>
@@ -5744,7 +5716,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>233</v>
       </c>
@@ -5767,7 +5739,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
         <v>234</v>
       </c>
@@ -5790,7 +5762,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
         <v>235</v>
       </c>
@@ -5813,7 +5785,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>236</v>
       </c>
@@ -5836,7 +5808,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>237</v>
       </c>

--- a/ch_02_pandas/ch_02.xlsx
+++ b/ch_02_pandas/ch_02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_02_pandas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E7D40BD-D687-4419-9C90-BB9448128F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8B0ADD-7FD0-4D00-9553-D7AF5065A4E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,20 @@
     <sheet name="nyc" sheetId="1" r:id="rId1"/>
     <sheet name="sales" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -41,9 +54,6 @@
     <t>Queens</t>
   </si>
   <si>
-    <t>Bronx</t>
-  </si>
-  <si>
     <t>Staten Island</t>
   </si>
   <si>
@@ -735,6 +745,9 @@
   </si>
   <si>
     <t>ORD-0200</t>
+  </si>
+  <si>
+    <t>The Bronx</t>
   </si>
 </sst>
 </file>
@@ -1154,40 +1167,40 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="3">
-        <v>1694251</v>
+        <v>2736074</v>
       </c>
       <c r="C2">
-        <v>22.83</v>
+        <v>69.37</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="3">
-        <v>2736074</v>
+        <v>2405464</v>
       </c>
       <c r="C3">
-        <v>69.37</v>
+        <v>108.53</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>2405464</v>
+        <v>1694251</v>
       </c>
       <c r="C4">
-        <v>108.53</v>
+        <v>22.83</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>237</v>
       </c>
       <c r="B5" s="3">
         <v>1472654</v>
@@ -1198,7 +1211,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" s="3">
         <v>495747</v>
@@ -1228,36 +1241,36 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
       </c>
       <c r="D2">
         <v>68.760000000000005</v>
@@ -1269,18 +1282,18 @@
         <v>37</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3">
         <v>115.2</v>
@@ -1292,18 +1305,18 @@
         <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4">
         <v>69.900000000000006</v>
@@ -1315,18 +1328,18 @@
         <v>63</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
         <v>23</v>
       </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5">
         <v>15.35</v>
@@ -1338,18 +1351,18 @@
         <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6">
         <v>479.68</v>
@@ -1361,18 +1374,18 @@
         <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7">
         <v>14.7</v>
@@ -1384,18 +1397,18 @@
         <v>51</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
         <v>31</v>
       </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8">
         <v>28.5</v>
@@ -1407,18 +1420,18 @@
         <v>45</v>
       </c>
       <c r="G8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9">
         <v>392.21</v>
@@ -1430,18 +1443,18 @@
         <v>36</v>
       </c>
       <c r="G9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
         <v>35</v>
       </c>
-      <c r="B10" t="s">
-        <v>36</v>
-      </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10">
         <v>9.81</v>
@@ -1453,18 +1466,18 @@
         <v>35</v>
       </c>
       <c r="G10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
         <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>17</v>
       </c>
       <c r="D11">
         <v>506.85</v>
@@ -1476,18 +1489,18 @@
         <v>56</v>
       </c>
       <c r="G11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12">
         <v>49.5</v>
@@ -1499,18 +1512,18 @@
         <v>36</v>
       </c>
       <c r="G12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D13">
         <v>415.36</v>
@@ -1522,18 +1535,18 @@
         <v>47</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s">
         <v>40</v>
       </c>
-      <c r="B14" t="s">
-        <v>41</v>
-      </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D14">
         <v>209.47</v>
@@ -1545,18 +1558,18 @@
         <v>47</v>
       </c>
       <c r="G14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
         <v>42</v>
       </c>
-      <c r="B15" t="s">
-        <v>43</v>
-      </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D15">
         <v>91.32</v>
@@ -1568,18 +1581,18 @@
         <v>56</v>
       </c>
       <c r="G15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" t="s">
         <v>44</v>
       </c>
-      <c r="B16" t="s">
-        <v>45</v>
-      </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D16">
         <v>321.5</v>
@@ -1591,18 +1604,18 @@
         <v>54</v>
       </c>
       <c r="G16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D17">
         <v>323.04000000000002</v>
@@ -1614,18 +1627,18 @@
         <v>60</v>
       </c>
       <c r="G17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D18">
         <v>14.07</v>
@@ -1637,18 +1650,18 @@
         <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D19">
         <v>626.45000000000005</v>
@@ -1660,18 +1673,18 @@
         <v>29</v>
       </c>
       <c r="G19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D20">
         <v>486.65</v>
@@ -1683,18 +1696,18 @@
         <v>54</v>
       </c>
       <c r="G20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21">
         <v>31.23</v>
@@ -1706,18 +1719,18 @@
         <v>45</v>
       </c>
       <c r="G21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" t="s">
         <v>16</v>
-      </c>
-      <c r="C22" t="s">
-        <v>17</v>
       </c>
       <c r="D22">
         <v>499.21</v>
@@ -1729,18 +1742,18 @@
         <v>23</v>
       </c>
       <c r="G22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" t="s">
         <v>53</v>
       </c>
-      <c r="B23" t="s">
-        <v>54</v>
-      </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D23">
         <v>4.78</v>
@@ -1752,18 +1765,18 @@
         <v>27</v>
       </c>
       <c r="G23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" t="s">
         <v>55</v>
       </c>
-      <c r="B24" t="s">
-        <v>56</v>
-      </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D24">
         <v>388.77</v>
@@ -1775,18 +1788,18 @@
         <v>64</v>
       </c>
       <c r="G24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D25">
         <v>43.88</v>
@@ -1798,18 +1811,18 @@
         <v>35</v>
       </c>
       <c r="G25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" t="s">
         <v>58</v>
       </c>
-      <c r="B26" t="s">
-        <v>59</v>
-      </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D26">
         <v>584.71</v>
@@ -1821,18 +1834,18 @@
         <v>64</v>
       </c>
       <c r="G26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D27">
         <v>140.75</v>
@@ -1844,18 +1857,18 @@
         <v>26</v>
       </c>
       <c r="G27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D28">
         <v>129.6</v>
@@ -1867,18 +1880,18 @@
         <v>62</v>
       </c>
       <c r="G28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D29">
         <v>58.66</v>
@@ -1890,18 +1903,18 @@
         <v>39</v>
       </c>
       <c r="G29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D30">
         <v>298.7</v>
@@ -1913,18 +1926,18 @@
         <v>52</v>
       </c>
       <c r="G30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" t="s">
         <v>64</v>
       </c>
-      <c r="B31" t="s">
-        <v>65</v>
-      </c>
       <c r="C31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D31">
         <v>193.29</v>
@@ -1936,18 +1949,18 @@
         <v>51</v>
       </c>
       <c r="G31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" t="s">
         <v>16</v>
-      </c>
-      <c r="C32" t="s">
-        <v>17</v>
       </c>
       <c r="D32">
         <v>95.46</v>
@@ -1959,18 +1972,18 @@
         <v>28</v>
       </c>
       <c r="G32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D33">
         <v>22.25</v>
@@ -1982,18 +1995,18 @@
         <v>51</v>
       </c>
       <c r="G33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C34" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D34">
         <v>6.7</v>
@@ -2005,18 +2018,18 @@
         <v>22</v>
       </c>
       <c r="G34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D35">
         <v>218.05</v>
@@ -2028,18 +2041,18 @@
         <v>35</v>
       </c>
       <c r="G35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D36">
         <v>26.02</v>
@@ -2051,18 +2064,18 @@
         <v>38</v>
       </c>
       <c r="G36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37" t="s">
         <v>71</v>
       </c>
-      <c r="B37" t="s">
-        <v>72</v>
-      </c>
       <c r="C37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D37">
         <v>35.44</v>
@@ -2074,18 +2087,18 @@
         <v>64</v>
       </c>
       <c r="G37" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B38" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D38">
         <v>48.5</v>
@@ -2097,18 +2110,18 @@
         <v>56</v>
       </c>
       <c r="G38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D39">
         <v>251.47</v>
@@ -2120,18 +2133,18 @@
         <v>32</v>
       </c>
       <c r="G39" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
+        <v>74</v>
+      </c>
+      <c r="B40" t="s">
         <v>75</v>
       </c>
-      <c r="B40" t="s">
-        <v>76</v>
-      </c>
       <c r="C40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D40">
         <v>307.64</v>
@@ -2143,18 +2156,18 @@
         <v>47</v>
       </c>
       <c r="G40" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D41">
         <v>307.39999999999998</v>
@@ -2166,18 +2179,18 @@
         <v>27</v>
       </c>
       <c r="G41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D42">
         <v>751.03</v>
@@ -2189,18 +2202,18 @@
         <v>64</v>
       </c>
       <c r="G42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B43" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C43" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D43">
         <v>34.24</v>
@@ -2212,18 +2225,18 @@
         <v>51</v>
       </c>
       <c r="G43" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B44" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D44">
         <v>242.69</v>
@@ -2235,18 +2248,18 @@
         <v>28</v>
       </c>
       <c r="G44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B45" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C45" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D45">
         <v>46.8</v>
@@ -2258,18 +2271,18 @@
         <v>37</v>
       </c>
       <c r="G45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D46">
         <v>508.76</v>
@@ -2281,18 +2294,18 @@
         <v>22</v>
       </c>
       <c r="G46" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B47" t="s">
+        <v>15</v>
+      </c>
+      <c r="C47" t="s">
         <v>16</v>
-      </c>
-      <c r="C47" t="s">
-        <v>17</v>
       </c>
       <c r="D47">
         <v>754.2</v>
@@ -2304,18 +2317,18 @@
         <v>38</v>
       </c>
       <c r="G47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B48" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C48" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D48">
         <v>254.26</v>
@@ -2327,18 +2340,18 @@
         <v>35</v>
       </c>
       <c r="G48" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C49" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D49">
         <v>429.06</v>
@@ -2350,18 +2363,18 @@
         <v>25</v>
       </c>
       <c r="G49" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B50" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C50" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D50">
         <v>2.17</v>
@@ -2373,18 +2386,18 @@
         <v>62</v>
       </c>
       <c r="G50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B51" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C51" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D51">
         <v>35.869999999999997</v>
@@ -2396,18 +2409,18 @@
         <v>22</v>
       </c>
       <c r="G51" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B52" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D52">
         <v>459.19</v>
@@ -2419,18 +2432,18 @@
         <v>59</v>
       </c>
       <c r="G52" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B53" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C53" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D53">
         <v>198.21</v>
@@ -2442,18 +2455,18 @@
         <v>44</v>
       </c>
       <c r="G53" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B54" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C54" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D54">
         <v>395.56</v>
@@ -2465,18 +2478,18 @@
         <v>61</v>
       </c>
       <c r="G54" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B55" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C55" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D55">
         <v>488.7</v>
@@ -2488,18 +2501,18 @@
         <v>48</v>
       </c>
       <c r="G55" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C56" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D56">
         <v>40.51</v>
@@ -2511,18 +2524,18 @@
         <v>39</v>
       </c>
       <c r="G56" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B57" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C57" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D57">
         <v>43.21</v>
@@ -2534,18 +2547,18 @@
         <v>34</v>
       </c>
       <c r="G57" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B58" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C58" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D58">
         <v>12.7</v>
@@ -2557,18 +2570,18 @@
         <v>47</v>
       </c>
       <c r="G58" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B59" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C59" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D59">
         <v>32.79</v>
@@ -2580,18 +2593,18 @@
         <v>65</v>
       </c>
       <c r="G59" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B60" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C60" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D60">
         <v>441.59</v>
@@ -2603,18 +2616,18 @@
         <v>33</v>
       </c>
       <c r="G60" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B61" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C61" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D61">
         <v>308.37</v>
@@ -2626,18 +2639,18 @@
         <v>42</v>
       </c>
       <c r="G61" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B62" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C62" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D62">
         <v>452.26</v>
@@ -2649,18 +2662,18 @@
         <v>38</v>
       </c>
       <c r="G62" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B63" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C63" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D63">
         <v>565.14</v>
@@ -2672,18 +2685,18 @@
         <v>45</v>
       </c>
       <c r="G63" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B64" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C64" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D64">
         <v>17.07</v>
@@ -2695,18 +2708,18 @@
         <v>41</v>
       </c>
       <c r="G64" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B65" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C65" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D65">
         <v>35.47</v>
@@ -2718,18 +2731,18 @@
         <v>30</v>
       </c>
       <c r="G65" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B66" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C66" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D66">
         <v>31.54</v>
@@ -2738,18 +2751,18 @@
         <v>5</v>
       </c>
       <c r="G66" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B67" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C67" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D67">
         <v>22.63</v>
@@ -2761,18 +2774,18 @@
         <v>60</v>
       </c>
       <c r="G67" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B68" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C68" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D68">
         <v>26.54</v>
@@ -2784,18 +2797,18 @@
         <v>64</v>
       </c>
       <c r="G68" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B69" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C69" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D69">
         <v>301.39</v>
@@ -2807,18 +2820,18 @@
         <v>65</v>
       </c>
       <c r="G69" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B70" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C70" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D70">
         <v>46.95</v>
@@ -2830,18 +2843,18 @@
         <v>61</v>
       </c>
       <c r="G70" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B71" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C71" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D71">
         <v>11.33</v>
@@ -2853,18 +2866,18 @@
         <v>53</v>
       </c>
       <c r="G71" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B72" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72" t="s">
         <v>16</v>
-      </c>
-      <c r="C72" t="s">
-        <v>17</v>
       </c>
       <c r="D72">
         <v>719.49</v>
@@ -2876,18 +2889,18 @@
         <v>49</v>
       </c>
       <c r="G72" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B73" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C73" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D73">
         <v>398.41</v>
@@ -2899,18 +2912,18 @@
         <v>37</v>
       </c>
       <c r="G73" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B74" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C74" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D74">
         <v>342.1</v>
@@ -2922,18 +2935,18 @@
         <v>60</v>
       </c>
       <c r="G74" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B75" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C75" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D75">
         <v>41.12</v>
@@ -2945,18 +2958,18 @@
         <v>49</v>
       </c>
       <c r="G75" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B76" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C76" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D76">
         <v>238.78</v>
@@ -2968,18 +2981,18 @@
         <v>62</v>
       </c>
       <c r="G76" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B77" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C77" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D77">
         <v>15.18</v>
@@ -2991,18 +3004,18 @@
         <v>40</v>
       </c>
       <c r="G77" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B78" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78" t="s">
         <v>16</v>
-      </c>
-      <c r="C78" t="s">
-        <v>17</v>
       </c>
       <c r="D78">
         <v>153.78</v>
@@ -3014,18 +3027,18 @@
         <v>46</v>
       </c>
       <c r="G78" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B79" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C79" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D79">
         <v>218.61</v>
@@ -3037,18 +3050,18 @@
         <v>51</v>
       </c>
       <c r="G79" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B80" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C80" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D80">
         <v>45.43</v>
@@ -3060,18 +3073,18 @@
         <v>23</v>
       </c>
       <c r="G80" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B81" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C81" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D81">
         <v>2.2799999999999998</v>
@@ -3083,18 +3096,18 @@
         <v>41</v>
       </c>
       <c r="G81" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B82" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C82" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D82">
         <v>37.880000000000003</v>
@@ -3106,18 +3119,18 @@
         <v>60</v>
       </c>
       <c r="G82" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B83" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C83" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D83">
         <v>25.31</v>
@@ -3129,18 +3142,18 @@
         <v>43</v>
       </c>
       <c r="G83" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B84" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C84" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D84">
         <v>680.38</v>
@@ -3152,18 +3165,18 @@
         <v>61</v>
       </c>
       <c r="G84" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B85" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C85" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D85">
         <v>547.25</v>
@@ -3175,18 +3188,18 @@
         <v>63</v>
       </c>
       <c r="G85" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B86" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C86" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D86">
         <v>148.57</v>
@@ -3198,18 +3211,18 @@
         <v>35</v>
       </c>
       <c r="G86" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B87" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C87" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D87">
         <v>38.1</v>
@@ -3221,18 +3234,18 @@
         <v>38</v>
       </c>
       <c r="G87" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B88" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C88" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D88">
         <v>89.06</v>
@@ -3244,18 +3257,18 @@
         <v>36</v>
       </c>
       <c r="G88" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B89" t="s">
+        <v>15</v>
+      </c>
+      <c r="C89" t="s">
         <v>16</v>
-      </c>
-      <c r="C89" t="s">
-        <v>17</v>
       </c>
       <c r="D89">
         <v>615.66999999999996</v>
@@ -3267,18 +3280,18 @@
         <v>34</v>
       </c>
       <c r="G89" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B90" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C90" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D90">
         <v>249.94</v>
@@ -3290,18 +3303,18 @@
         <v>58</v>
       </c>
       <c r="G90" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B91" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C91" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D91">
         <v>10.050000000000001</v>
@@ -3313,18 +3326,18 @@
         <v>29</v>
       </c>
       <c r="G91" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B92" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C92" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D92">
         <v>29.78</v>
@@ -3336,18 +3349,18 @@
         <v>58</v>
       </c>
       <c r="G92" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B93" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C93" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D93">
         <v>5.65</v>
@@ -3359,18 +3372,18 @@
         <v>28</v>
       </c>
       <c r="G93" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B94" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C94" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D94">
         <v>654.15</v>
@@ -3382,18 +3395,18 @@
         <v>24</v>
       </c>
       <c r="G94" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B95" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C95" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D95">
         <v>26.29</v>
@@ -3405,18 +3418,18 @@
         <v>22</v>
       </c>
       <c r="G95" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B96" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C96" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D96">
         <v>481.37</v>
@@ -3428,18 +3441,18 @@
         <v>31</v>
       </c>
       <c r="G96" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B97" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C97" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D97">
         <v>511.93</v>
@@ -3451,18 +3464,18 @@
         <v>52</v>
       </c>
       <c r="G97" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B98" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C98" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D98">
         <v>291.73</v>
@@ -3474,18 +3487,18 @@
         <v>27</v>
       </c>
       <c r="G98" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B99" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C99" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D99">
         <v>31.3</v>
@@ -3497,18 +3510,18 @@
         <v>43</v>
       </c>
       <c r="G99" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B100" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C100" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D100">
         <v>125.76</v>
@@ -3520,18 +3533,18 @@
         <v>43</v>
       </c>
       <c r="G100" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B101" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C101" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D101">
         <v>2.4900000000000002</v>
@@ -3543,18 +3556,18 @@
         <v>27</v>
       </c>
       <c r="G101" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B102" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C102" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D102">
         <v>567.96</v>
@@ -3566,18 +3579,18 @@
         <v>50</v>
       </c>
       <c r="G102" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B103" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C103" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D103">
         <v>353.6</v>
@@ -3589,18 +3602,18 @@
         <v>64</v>
       </c>
       <c r="G103" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B104" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C104" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D104">
         <v>369.13</v>
@@ -3612,18 +3625,18 @@
         <v>43</v>
       </c>
       <c r="G104" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B105" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C105" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D105">
         <v>13.07</v>
@@ -3635,18 +3648,18 @@
         <v>42</v>
       </c>
       <c r="G105" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B106" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C106" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D106">
         <v>193.66</v>
@@ -3658,18 +3671,18 @@
         <v>39</v>
       </c>
       <c r="G106" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B107" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C107" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D107">
         <v>262.25</v>
@@ -3681,18 +3694,18 @@
         <v>34</v>
       </c>
       <c r="G107" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B108" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C108" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D108">
         <v>35.979999999999997</v>
@@ -3704,18 +3717,18 @@
         <v>39</v>
       </c>
       <c r="G108" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B109" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C109" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D109">
         <v>32.619999999999997</v>
@@ -3727,18 +3740,18 @@
         <v>28</v>
       </c>
       <c r="G109" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B110" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C110" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D110">
         <v>23.14</v>
@@ -3750,18 +3763,18 @@
         <v>25</v>
       </c>
       <c r="G110" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B111" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C111" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D111">
         <v>215.34</v>
@@ -3773,18 +3786,18 @@
         <v>58</v>
       </c>
       <c r="G111" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B112" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C112" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D112">
         <v>475.83</v>
@@ -3796,18 +3809,18 @@
         <v>37</v>
       </c>
       <c r="G112" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B113" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C113" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D113">
         <v>643.05999999999995</v>
@@ -3819,18 +3832,18 @@
         <v>55</v>
       </c>
       <c r="G113" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B114" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C114" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D114">
         <v>49.52</v>
@@ -3842,18 +3855,18 @@
         <v>58</v>
       </c>
       <c r="G114" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B115" t="s">
+        <v>15</v>
+      </c>
+      <c r="C115" t="s">
         <v>16</v>
-      </c>
-      <c r="C115" t="s">
-        <v>17</v>
       </c>
       <c r="D115">
         <v>760.69</v>
@@ -3865,18 +3878,18 @@
         <v>62</v>
       </c>
       <c r="G115" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B116" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C116" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D116">
         <v>107.56</v>
@@ -3888,18 +3901,18 @@
         <v>32</v>
       </c>
       <c r="G116" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B117" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C117" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D117">
         <v>268.44</v>
@@ -3911,18 +3924,18 @@
         <v>40</v>
       </c>
       <c r="G117" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B118" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C118" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D118">
         <v>34.99</v>
@@ -3934,18 +3947,18 @@
         <v>62</v>
       </c>
       <c r="G118" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B119" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C119" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D119">
         <v>79.52</v>
@@ -3957,18 +3970,18 @@
         <v>63</v>
       </c>
       <c r="G119" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B120" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C120" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D120">
         <v>53.33</v>
@@ -3980,18 +3993,18 @@
         <v>60</v>
       </c>
       <c r="G120" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B121" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C121" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D121">
         <v>7.97</v>
@@ -4003,18 +4016,18 @@
         <v>47</v>
       </c>
       <c r="G121" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B122" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C122" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D122">
         <v>5.86</v>
@@ -4026,18 +4039,18 @@
         <v>49</v>
       </c>
       <c r="G122" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B123" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C123" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D123">
         <v>133.74</v>
@@ -4049,18 +4062,18 @@
         <v>59</v>
       </c>
       <c r="G123" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B124" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C124" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D124">
         <v>482.19</v>
@@ -4072,18 +4085,18 @@
         <v>52</v>
       </c>
       <c r="G124" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B125" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C125" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D125">
         <v>49.85</v>
@@ -4095,18 +4108,18 @@
         <v>62</v>
       </c>
       <c r="G125" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B126" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C126" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D126">
         <v>21.6</v>
@@ -4118,18 +4131,18 @@
         <v>64</v>
       </c>
       <c r="G126" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B127" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C127" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D127">
         <v>15.83</v>
@@ -4141,18 +4154,18 @@
         <v>57</v>
       </c>
       <c r="G127" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B128" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C128" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D128">
         <v>7.56</v>
@@ -4161,18 +4174,18 @@
         <v>7</v>
       </c>
       <c r="G128" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B129" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C129" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D129">
         <v>359.94</v>
@@ -4184,18 +4197,18 @@
         <v>55</v>
       </c>
       <c r="G129" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B130" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C130" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D130">
         <v>619.99</v>
@@ -4207,18 +4220,18 @@
         <v>39</v>
       </c>
       <c r="G130" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B131" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C131" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D131">
         <v>7.83</v>
@@ -4230,18 +4243,18 @@
         <v>37</v>
       </c>
       <c r="G131" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B132" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C132" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D132">
         <v>218.8</v>
@@ -4253,18 +4266,18 @@
         <v>29</v>
       </c>
       <c r="G132" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B133" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C133" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D133">
         <v>468.01</v>
@@ -4276,18 +4289,18 @@
         <v>54</v>
       </c>
       <c r="G133" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B134" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C134" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D134">
         <v>13.7</v>
@@ -4299,18 +4312,18 @@
         <v>31</v>
       </c>
       <c r="G134" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B135" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C135" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D135">
         <v>698.02</v>
@@ -4322,18 +4335,18 @@
         <v>48</v>
       </c>
       <c r="G135" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B136" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C136" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D136">
         <v>15.58</v>
@@ -4345,18 +4358,18 @@
         <v>59</v>
       </c>
       <c r="G136" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B137" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C137" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D137">
         <v>280.83</v>
@@ -4368,18 +4381,18 @@
         <v>43</v>
       </c>
       <c r="G137" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B138" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C138" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D138">
         <v>43.74</v>
@@ -4391,18 +4404,18 @@
         <v>58</v>
       </c>
       <c r="G138" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B139" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C139" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D139">
         <v>17.27</v>
@@ -4414,18 +4427,18 @@
         <v>46</v>
       </c>
       <c r="G139" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B140" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C140" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D140">
         <v>421.5</v>
@@ -4437,18 +4450,18 @@
         <v>30</v>
       </c>
       <c r="G140" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B141" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C141" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D141">
         <v>72.36</v>
@@ -4460,18 +4473,18 @@
         <v>22</v>
       </c>
       <c r="G141" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B142" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C142" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D142">
         <v>106.12</v>
@@ -4483,18 +4496,18 @@
         <v>43</v>
       </c>
       <c r="G142" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B143" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C143" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D143">
         <v>429.86</v>
@@ -4506,18 +4519,18 @@
         <v>46</v>
       </c>
       <c r="G143" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B144" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C144" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D144">
         <v>3.72</v>
@@ -4529,18 +4542,18 @@
         <v>37</v>
       </c>
       <c r="G144" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B145" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C145" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D145">
         <v>231.14</v>
@@ -4552,18 +4565,18 @@
         <v>62</v>
       </c>
       <c r="G145" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B146" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C146" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D146">
         <v>454.13</v>
@@ -4575,18 +4588,18 @@
         <v>42</v>
       </c>
       <c r="G146" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B147" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C147" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D147">
         <v>8.99</v>
@@ -4598,18 +4611,18 @@
         <v>48</v>
       </c>
       <c r="G147" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B148" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C148" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D148">
         <v>62.51</v>
@@ -4621,18 +4634,18 @@
         <v>61</v>
       </c>
       <c r="G148" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B149" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C149" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D149">
         <v>224.14</v>
@@ -4641,18 +4654,18 @@
         <v>5</v>
       </c>
       <c r="G149" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B150" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C150" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D150">
         <v>34.53</v>
@@ -4664,18 +4677,18 @@
         <v>26</v>
       </c>
       <c r="G150" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B151" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C151" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D151">
         <v>529.20000000000005</v>
@@ -4687,18 +4700,18 @@
         <v>38</v>
       </c>
       <c r="G151" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B152" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C152" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D152">
         <v>7.12</v>
@@ -4710,18 +4723,18 @@
         <v>58</v>
       </c>
       <c r="G152" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B153" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C153" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D153">
         <v>66.45</v>
@@ -4733,18 +4746,18 @@
         <v>39</v>
       </c>
       <c r="G153" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B154" t="s">
+        <v>15</v>
+      </c>
+      <c r="C154" t="s">
         <v>16</v>
-      </c>
-      <c r="C154" t="s">
-        <v>17</v>
       </c>
       <c r="D154">
         <v>732.96</v>
@@ -4756,18 +4769,18 @@
         <v>40</v>
       </c>
       <c r="G154" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B155" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C155" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D155">
         <v>32.56</v>
@@ -4779,18 +4792,18 @@
         <v>38</v>
       </c>
       <c r="G155" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B156" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C156" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D156">
         <v>521.19000000000005</v>
@@ -4799,18 +4812,18 @@
         <v>1</v>
       </c>
       <c r="G156" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B157" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C157" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D157">
         <v>6.33</v>
@@ -4822,18 +4835,18 @@
         <v>42</v>
       </c>
       <c r="G157" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B158" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C158" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D158">
         <v>441.32</v>
@@ -4845,18 +4858,18 @@
         <v>55</v>
       </c>
       <c r="G158" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B159" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C159" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D159">
         <v>459.17</v>
@@ -4868,18 +4881,18 @@
         <v>40</v>
       </c>
       <c r="G159" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B160" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C160" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D160">
         <v>482.37</v>
@@ -4891,18 +4904,18 @@
         <v>36</v>
       </c>
       <c r="G160" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B161" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C161" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D161">
         <v>19.559999999999999</v>
@@ -4914,18 +4927,18 @@
         <v>22</v>
       </c>
       <c r="G161" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B162" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C162" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D162">
         <v>30.06</v>
@@ -4937,18 +4950,18 @@
         <v>28</v>
       </c>
       <c r="G162" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B163" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C163" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D163">
         <v>296</v>
@@ -4960,18 +4973,18 @@
         <v>36</v>
       </c>
       <c r="G163" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B164" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C164" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D164">
         <v>33.159999999999997</v>
@@ -4980,18 +4993,18 @@
         <v>2</v>
       </c>
       <c r="G164" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B165" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C165" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D165">
         <v>6.67</v>
@@ -5003,18 +5016,18 @@
         <v>30</v>
       </c>
       <c r="G165" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B166" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C166" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D166">
         <v>364.35</v>
@@ -5026,18 +5039,18 @@
         <v>48</v>
       </c>
       <c r="G166" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B167" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C167" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D167">
         <v>754.29</v>
@@ -5049,18 +5062,18 @@
         <v>24</v>
       </c>
       <c r="G167" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B168" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C168" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D168">
         <v>43.06</v>
@@ -5072,18 +5085,18 @@
         <v>65</v>
       </c>
       <c r="G168" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B169" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C169" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D169">
         <v>95.41</v>
@@ -5095,18 +5108,18 @@
         <v>34</v>
       </c>
       <c r="G169" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B170" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C170" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D170">
         <v>33.81</v>
@@ -5118,18 +5131,18 @@
         <v>23</v>
       </c>
       <c r="G170" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B171" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C171" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D171">
         <v>122.47</v>
@@ -5141,18 +5154,18 @@
         <v>35</v>
       </c>
       <c r="G171" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B172" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C172" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D172">
         <v>392.83</v>
@@ -5164,18 +5177,18 @@
         <v>22</v>
       </c>
       <c r="G172" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B173" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C173" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D173">
         <v>144.06</v>
@@ -5184,18 +5197,18 @@
         <v>3</v>
       </c>
       <c r="G173" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B174" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C174" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D174">
         <v>400.24</v>
@@ -5207,18 +5220,18 @@
         <v>59</v>
       </c>
       <c r="G174" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B175" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C175" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D175">
         <v>377.32</v>
@@ -5230,18 +5243,18 @@
         <v>29</v>
       </c>
       <c r="G175" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B176" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C176" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D176">
         <v>30.5</v>
@@ -5253,18 +5266,18 @@
         <v>54</v>
       </c>
       <c r="G176" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B177" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C177" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D177">
         <v>276.22000000000003</v>
@@ -5276,18 +5289,18 @@
         <v>25</v>
       </c>
       <c r="G177" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B178" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C178" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D178">
         <v>25.53</v>
@@ -5299,18 +5312,18 @@
         <v>26</v>
       </c>
       <c r="G178" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B179" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C179" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D179">
         <v>84.94</v>
@@ -5322,18 +5335,18 @@
         <v>62</v>
       </c>
       <c r="G179" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B180" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C180" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D180">
         <v>27.47</v>
@@ -5345,18 +5358,18 @@
         <v>54</v>
       </c>
       <c r="G180" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B181" t="s">
+        <v>15</v>
+      </c>
+      <c r="C181" t="s">
         <v>16</v>
-      </c>
-      <c r="C181" t="s">
-        <v>17</v>
       </c>
       <c r="D181">
         <v>689.59</v>
@@ -5368,18 +5381,18 @@
         <v>35</v>
       </c>
       <c r="G181" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B182" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C182" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D182">
         <v>41.72</v>
@@ -5391,18 +5404,18 @@
         <v>48</v>
       </c>
       <c r="G182" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B183" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C183" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D183">
         <v>19.97</v>
@@ -5414,18 +5427,18 @@
         <v>65</v>
       </c>
       <c r="G183" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B184" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C184" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D184">
         <v>230.14</v>
@@ -5437,18 +5450,18 @@
         <v>30</v>
       </c>
       <c r="G184" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B185" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C185" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D185">
         <v>297.23</v>
@@ -5460,18 +5473,18 @@
         <v>48</v>
       </c>
       <c r="G185" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B186" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C186" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D186">
         <v>48.48</v>
@@ -5483,18 +5496,18 @@
         <v>41</v>
       </c>
       <c r="G186" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B187" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C187" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D187">
         <v>336.95</v>
@@ -5506,18 +5519,18 @@
         <v>28</v>
       </c>
       <c r="G187" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B188" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C188" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D188">
         <v>297.7</v>
@@ -5529,18 +5542,18 @@
         <v>57</v>
       </c>
       <c r="G188" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B189" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C189" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D189">
         <v>69.69</v>
@@ -5552,18 +5565,18 @@
         <v>23</v>
       </c>
       <c r="G189" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B190" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C190" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D190">
         <v>18.850000000000001</v>
@@ -5575,18 +5588,18 @@
         <v>31</v>
       </c>
       <c r="G190" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B191" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C191" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D191">
         <v>68.58</v>
@@ -5598,18 +5611,18 @@
         <v>35</v>
       </c>
       <c r="G191" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B192" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C192" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D192">
         <v>173.03</v>
@@ -5621,18 +5634,18 @@
         <v>58</v>
       </c>
       <c r="G192" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B193" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C193" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D193">
         <v>383.36</v>
@@ -5644,18 +5657,18 @@
         <v>65</v>
       </c>
       <c r="G193" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B194" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C194" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D194">
         <v>31.14</v>
@@ -5667,18 +5680,18 @@
         <v>39</v>
       </c>
       <c r="G194" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B195" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C195" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D195">
         <v>7.32</v>
@@ -5690,18 +5703,18 @@
         <v>53</v>
       </c>
       <c r="G195" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B196" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C196" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D196">
         <v>492.61</v>
@@ -5713,18 +5726,18 @@
         <v>22</v>
       </c>
       <c r="G196" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B197" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C197" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D197">
         <v>162.49</v>
@@ -5736,18 +5749,18 @@
         <v>22</v>
       </c>
       <c r="G197" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B198" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C198" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D198">
         <v>277.98</v>
@@ -5759,18 +5772,18 @@
         <v>54</v>
       </c>
       <c r="G198" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B199" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C199" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D199">
         <v>21.06</v>
@@ -5782,18 +5795,18 @@
         <v>49</v>
       </c>
       <c r="G199" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B200" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C200" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D200">
         <v>22.61</v>
@@ -5805,18 +5818,18 @@
         <v>62</v>
       </c>
       <c r="G200" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B201" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C201" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D201">
         <v>106.64</v>
@@ -5828,7 +5841,7 @@
         <v>51</v>
       </c>
       <c r="G201" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
